--- a/amostras/principal/P06/matriz_rastreabilidade_P06.xlsx
+++ b/amostras/principal/P06/matriz_rastreabilidade_P06.xlsx
@@ -634,6 +634,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -871,6 +872,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -928,6 +930,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -985,6 +988,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1042,6 +1046,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1099,6 +1104,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1156,6 +1162,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -2233,6 +2240,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -2290,6 +2298,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Nenhum</t>
